--- a/astro-site/public/dl/plan-negocio-paellero-eventos/checklist-apertura-paellero-eventos.xlsx
+++ b/astro-site/public/dl/plan-negocio-paellero-eventos/checklist-apertura-paellero-eventos.xlsx
@@ -19,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="6">
+  <fonts count="9">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -54,6 +54,22 @@
     <font>
       <name val="Calibri"/>
       <color rgb="000A0908"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <i val="1"/>
+      <color rgb="00595959"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
       <sz val="11"/>
     </font>
   </fonts>
@@ -101,7 +117,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -118,10 +134,37 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="9" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
+  <dxfs count="1">
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color rgb="00006100"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00C6EFCE"/>
+          <bgColor rgb="00C6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
@@ -504,11 +547,44 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>6 fases · 110 hitos · adaptado al modelo itinerante eventos · Tachar al avanzar</t>
-        </is>
-      </c>
-    </row>
-    <row r="3"/>
+          <t>6 fases · 104 hitos · adaptado al modelo itinerante eventos · Tachar al avanzar</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="6" t="inlineStr">
+        <is>
+          <t>Marca ✓ al completar; N/A si no aplica</t>
+        </is>
+      </c>
+      <c r="D3" s="7" t="inlineStr">
+        <is>
+          <t>Progreso del checklist →</t>
+        </is>
+      </c>
+      <c r="E3" s="8">
+        <f>IFERROR(H3/J3,"")</f>
+        <v>0.0</v>
+      </c>
+      <c r="G3" s="7" t="inlineStr">
+        <is>
+          <t>Completados</t>
+        </is>
+      </c>
+      <c r="H3" s="9">
+        <f>COUNTIF(F6:F119,"✓")</f>
+        <v>0.0</v>
+      </c>
+      <c r="I3" s="7" t="inlineStr">
+        <is>
+          <t>Aplicables</t>
+        </is>
+      </c>
+      <c r="J3" s="9">
+        <f>COUNTIF(F6:F119,"✓")+COUNTIF(F6:F119,"☐")</f>
+        <v>104.0</v>
+      </c>
+    </row>
     <row r="4" ht="26" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -572,7 +648,11 @@
           <t>Día 1-3</t>
         </is>
       </c>
-      <c r="F6" s="5" t="inlineStr"/>
+      <c r="F6" s="10" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
@@ -598,7 +678,11 @@
           <t>Día 1</t>
         </is>
       </c>
-      <c r="F7" s="5" t="inlineStr"/>
+      <c r="F7" s="10" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
@@ -624,7 +708,11 @@
           <t>Día 1-7</t>
         </is>
       </c>
-      <c r="F8" s="5" t="inlineStr"/>
+      <c r="F8" s="10" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
@@ -650,7 +738,11 @@
           <t>Semana 1-2</t>
         </is>
       </c>
-      <c r="F9" s="5" t="inlineStr"/>
+      <c r="F9" s="10" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
@@ -676,7 +768,11 @@
           <t>Semana 1</t>
         </is>
       </c>
-      <c r="F10" s="5" t="inlineStr"/>
+      <c r="F10" s="10" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
@@ -702,7 +798,11 @@
           <t>Semana 2-4</t>
         </is>
       </c>
-      <c r="F11" s="5" t="inlineStr"/>
+      <c r="F11" s="10" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
@@ -728,7 +828,11 @@
           <t>Semana 2-4</t>
         </is>
       </c>
-      <c r="F12" s="5" t="inlineStr"/>
+      <c r="F12" s="10" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
@@ -754,7 +858,11 @@
           <t>Semana 1</t>
         </is>
       </c>
-      <c r="F13" s="5" t="inlineStr"/>
+      <c r="F13" s="10" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
@@ -780,7 +888,11 @@
           <t>Semana 2</t>
         </is>
       </c>
-      <c r="F14" s="5" t="inlineStr"/>
+      <c r="F14" s="10" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
@@ -806,7 +918,11 @@
           <t>Semana 1-2</t>
         </is>
       </c>
-      <c r="F15" s="5" t="inlineStr"/>
+      <c r="F15" s="10" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
@@ -832,7 +948,11 @@
           <t>Semana 2</t>
         </is>
       </c>
-      <c r="F16" s="5" t="inlineStr"/>
+      <c r="F16" s="10" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
@@ -858,7 +978,11 @@
           <t>Semana 2</t>
         </is>
       </c>
-      <c r="F17" s="5" t="inlineStr"/>
+      <c r="F17" s="10" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
@@ -884,7 +1008,11 @@
           <t>Semana 2</t>
         </is>
       </c>
-      <c r="F18" s="5" t="inlineStr"/>
+      <c r="F18" s="10" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
@@ -910,7 +1038,11 @@
           <t>Mes 1</t>
         </is>
       </c>
-      <c r="F19" s="5" t="inlineStr"/>
+      <c r="F19" s="10" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
@@ -936,7 +1068,11 @@
           <t>Día 1-7</t>
         </is>
       </c>
-      <c r="F20" s="5" t="inlineStr"/>
+      <c r="F20" s="10" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
@@ -962,7 +1098,11 @@
           <t>Día 1</t>
         </is>
       </c>
-      <c r="F21" s="5" t="inlineStr"/>
+      <c r="F21" s="10" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
@@ -988,7 +1128,11 @@
           <t>Trimestral</t>
         </is>
       </c>
-      <c r="F22" s="5" t="inlineStr"/>
+      <c r="F22" s="10" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
@@ -1014,7 +1158,11 @@
           <t>Trimestral</t>
         </is>
       </c>
-      <c r="F23" s="5" t="inlineStr"/>
+      <c r="F23" s="10" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
@@ -1040,7 +1188,11 @@
           <t>Anual</t>
         </is>
       </c>
-      <c r="F24" s="5" t="inlineStr"/>
+      <c r="F24" s="10" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
     </row>
     <row r="25"/>
     <row r="26" ht="22" customHeight="1">
@@ -1074,7 +1226,11 @@
           <t>Semana 2-4</t>
         </is>
       </c>
-      <c r="F27" s="5" t="inlineStr"/>
+      <c r="F27" s="10" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
@@ -1100,7 +1256,11 @@
           <t>Semana 2-4</t>
         </is>
       </c>
-      <c r="F28" s="5" t="inlineStr"/>
+      <c r="F28" s="10" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
@@ -1126,7 +1286,11 @@
           <t>Semana 2</t>
         </is>
       </c>
-      <c r="F29" s="5" t="inlineStr"/>
+      <c r="F29" s="10" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
@@ -1152,7 +1316,11 @@
           <t>Mes 2-3</t>
         </is>
       </c>
-      <c r="F30" s="5" t="inlineStr"/>
+      <c r="F30" s="10" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
@@ -1178,7 +1346,11 @@
           <t>Solo si aplica</t>
         </is>
       </c>
-      <c r="F31" s="5" t="inlineStr"/>
+      <c r="F31" s="10" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
@@ -1204,7 +1376,11 @@
           <t>Mes 1-2</t>
         </is>
       </c>
-      <c r="F32" s="5" t="inlineStr"/>
+      <c r="F32" s="10" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
@@ -1230,7 +1406,11 @@
           <t>Semana 2-4</t>
         </is>
       </c>
-      <c r="F33" s="5" t="inlineStr"/>
+      <c r="F33" s="10" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
@@ -1256,7 +1436,11 @@
           <t>Por evento</t>
         </is>
       </c>
-      <c r="F34" s="5" t="inlineStr"/>
+      <c r="F34" s="10" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
@@ -1282,7 +1466,11 @@
           <t>Mes 6+ si food truck</t>
         </is>
       </c>
-      <c r="F35" s="5" t="inlineStr"/>
+      <c r="F35" s="10" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
@@ -1308,7 +1496,11 @@
           <t>Por evento</t>
         </is>
       </c>
-      <c r="F36" s="5" t="inlineStr"/>
+      <c r="F36" s="10" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
     </row>
     <row r="37"/>
     <row r="38" ht="22" customHeight="1">
@@ -1342,7 +1534,11 @@
           <t>Mes 1</t>
         </is>
       </c>
-      <c r="F39" s="5" t="inlineStr"/>
+      <c r="F39" s="10" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="5" t="inlineStr">
@@ -1368,7 +1564,11 @@
           <t>Mes 1</t>
         </is>
       </c>
-      <c r="F40" s="5" t="inlineStr"/>
+      <c r="F40" s="10" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
@@ -1394,7 +1594,11 @@
           <t>Mes 1</t>
         </is>
       </c>
-      <c r="F41" s="5" t="inlineStr"/>
+      <c r="F41" s="10" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="5" t="inlineStr">
@@ -1420,7 +1624,11 @@
           <t>Mes 1</t>
         </is>
       </c>
-      <c r="F42" s="5" t="inlineStr"/>
+      <c r="F42" s="10" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="5" t="inlineStr">
@@ -1446,7 +1654,11 @@
           <t>Mes 1</t>
         </is>
       </c>
-      <c r="F43" s="5" t="inlineStr"/>
+      <c r="F43" s="10" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="5" t="inlineStr">
@@ -1472,7 +1684,11 @@
           <t>Mes 1</t>
         </is>
       </c>
-      <c r="F44" s="5" t="inlineStr"/>
+      <c r="F44" s="10" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="5" t="inlineStr">
@@ -1498,7 +1714,11 @@
           <t>Mes 1</t>
         </is>
       </c>
-      <c r="F45" s="5" t="inlineStr"/>
+      <c r="F45" s="10" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="5" t="inlineStr">
@@ -1524,7 +1744,11 @@
           <t>Mes 1</t>
         </is>
       </c>
-      <c r="F46" s="5" t="inlineStr"/>
+      <c r="F46" s="10" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="5" t="inlineStr">
@@ -1550,7 +1774,11 @@
           <t>Mes 1</t>
         </is>
       </c>
-      <c r="F47" s="5" t="inlineStr"/>
+      <c r="F47" s="10" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="5" t="inlineStr">
@@ -1576,7 +1804,11 @@
           <t>Mes 1</t>
         </is>
       </c>
-      <c r="F48" s="5" t="inlineStr"/>
+      <c r="F48" s="10" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="5" t="inlineStr">
@@ -1602,7 +1834,11 @@
           <t>Mes 1-2</t>
         </is>
       </c>
-      <c r="F49" s="5" t="inlineStr"/>
+      <c r="F49" s="10" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="5" t="inlineStr">
@@ -1628,7 +1864,11 @@
           <t>Mes 1-2</t>
         </is>
       </c>
-      <c r="F50" s="5" t="inlineStr"/>
+      <c r="F50" s="10" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="5" t="inlineStr">
@@ -1654,7 +1894,11 @@
           <t>Mes 1</t>
         </is>
       </c>
-      <c r="F51" s="5" t="inlineStr"/>
+      <c r="F51" s="10" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="5" t="inlineStr">
@@ -1680,7 +1924,11 @@
           <t>Mes 1</t>
         </is>
       </c>
-      <c r="F52" s="5" t="inlineStr"/>
+      <c r="F52" s="10" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="5" t="inlineStr">
@@ -1706,7 +1954,11 @@
           <t>Mes 1</t>
         </is>
       </c>
-      <c r="F53" s="5" t="inlineStr"/>
+      <c r="F53" s="10" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="5" t="inlineStr">
@@ -1732,7 +1984,11 @@
           <t>Mes 1</t>
         </is>
       </c>
-      <c r="F54" s="5" t="inlineStr"/>
+      <c r="F54" s="10" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="5" t="inlineStr">
@@ -1758,7 +2014,11 @@
           <t>Mes 1</t>
         </is>
       </c>
-      <c r="F55" s="5" t="inlineStr"/>
+      <c r="F55" s="10" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="5" t="inlineStr">
@@ -1784,7 +2044,11 @@
           <t>Mes 1</t>
         </is>
       </c>
-      <c r="F56" s="5" t="inlineStr"/>
+      <c r="F56" s="10" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="5" t="inlineStr">
@@ -1810,7 +2074,11 @@
           <t>Mes 1</t>
         </is>
       </c>
-      <c r="F57" s="5" t="inlineStr"/>
+      <c r="F57" s="10" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="5" t="inlineStr">
@@ -1836,7 +2104,11 @@
           <t>Mes 1-2</t>
         </is>
       </c>
-      <c r="F58" s="5" t="inlineStr"/>
+      <c r="F58" s="10" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="5" t="inlineStr">
@@ -1862,7 +2134,11 @@
           <t>Mes 1</t>
         </is>
       </c>
-      <c r="F59" s="5" t="inlineStr"/>
+      <c r="F59" s="10" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="5" t="inlineStr">
@@ -1888,7 +2164,11 @@
           <t>Mes 1</t>
         </is>
       </c>
-      <c r="F60" s="5" t="inlineStr"/>
+      <c r="F60" s="10" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="5" t="inlineStr">
@@ -1914,7 +2194,11 @@
           <t>Mes 1</t>
         </is>
       </c>
-      <c r="F61" s="5" t="inlineStr"/>
+      <c r="F61" s="10" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="5" t="inlineStr">
@@ -1940,7 +2224,11 @@
           <t>Mes 1</t>
         </is>
       </c>
-      <c r="F62" s="5" t="inlineStr"/>
+      <c r="F62" s="10" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="5" t="inlineStr">
@@ -1966,7 +2254,11 @@
           <t>Mes 1</t>
         </is>
       </c>
-      <c r="F63" s="5" t="inlineStr"/>
+      <c r="F63" s="10" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="5" t="inlineStr">
@@ -1992,7 +2284,11 @@
           <t>Mes 1</t>
         </is>
       </c>
-      <c r="F64" s="5" t="inlineStr"/>
+      <c r="F64" s="10" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="5" t="inlineStr">
@@ -2018,7 +2314,11 @@
           <t>Mes 1</t>
         </is>
       </c>
-      <c r="F65" s="5" t="inlineStr"/>
+      <c r="F65" s="10" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
     </row>
     <row r="66"/>
     <row r="67" ht="22" customHeight="1">
@@ -2052,7 +2352,11 @@
           <t>Mes 1</t>
         </is>
       </c>
-      <c r="F68" s="5" t="inlineStr"/>
+      <c r="F68" s="10" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="5" t="inlineStr">
@@ -2078,7 +2382,11 @@
           <t>Mes 1</t>
         </is>
       </c>
-      <c r="F69" s="5" t="inlineStr"/>
+      <c r="F69" s="10" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="5" t="inlineStr">
@@ -2104,7 +2412,11 @@
           <t>Mes 1-2</t>
         </is>
       </c>
-      <c r="F70" s="5" t="inlineStr"/>
+      <c r="F70" s="10" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="5" t="inlineStr">
@@ -2130,7 +2442,11 @@
           <t>Mes 1-2</t>
         </is>
       </c>
-      <c r="F71" s="5" t="inlineStr"/>
+      <c r="F71" s="10" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="5" t="inlineStr">
@@ -2156,7 +2472,11 @@
           <t>Mes 2</t>
         </is>
       </c>
-      <c r="F72" s="5" t="inlineStr"/>
+      <c r="F72" s="10" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="5" t="inlineStr">
@@ -2182,7 +2502,11 @@
           <t>Mes 1</t>
         </is>
       </c>
-      <c r="F73" s="5" t="inlineStr"/>
+      <c r="F73" s="10" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="5" t="inlineStr">
@@ -2208,7 +2532,11 @@
           <t>Mes 1-2</t>
         </is>
       </c>
-      <c r="F74" s="5" t="inlineStr"/>
+      <c r="F74" s="10" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="5" t="inlineStr">
@@ -2234,7 +2562,11 @@
           <t>Mes 1+</t>
         </is>
       </c>
-      <c r="F75" s="5" t="inlineStr"/>
+      <c r="F75" s="10" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="5" t="inlineStr">
@@ -2260,7 +2592,11 @@
           <t>Mes 2</t>
         </is>
       </c>
-      <c r="F76" s="5" t="inlineStr"/>
+      <c r="F76" s="10" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="5" t="inlineStr">
@@ -2286,7 +2622,11 @@
           <t>Mes 2+</t>
         </is>
       </c>
-      <c r="F77" s="5" t="inlineStr"/>
+      <c r="F77" s="10" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="5" t="inlineStr">
@@ -2312,7 +2652,11 @@
           <t>Mes 1</t>
         </is>
       </c>
-      <c r="F78" s="5" t="inlineStr"/>
+      <c r="F78" s="10" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="5" t="inlineStr">
@@ -2338,7 +2682,11 @@
           <t>Mes 2</t>
         </is>
       </c>
-      <c r="F79" s="5" t="inlineStr"/>
+      <c r="F79" s="10" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="5" t="inlineStr">
@@ -2364,7 +2712,11 @@
           <t>Mes 2</t>
         </is>
       </c>
-      <c r="F80" s="5" t="inlineStr"/>
+      <c r="F80" s="10" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="5" t="inlineStr">
@@ -2390,7 +2742,11 @@
           <t>Mes 2-3</t>
         </is>
       </c>
-      <c r="F81" s="5" t="inlineStr"/>
+      <c r="F81" s="10" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="5" t="inlineStr">
@@ -2416,7 +2772,11 @@
           <t>Mes 2</t>
         </is>
       </c>
-      <c r="F82" s="5" t="inlineStr"/>
+      <c r="F82" s="10" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="5" t="inlineStr">
@@ -2442,7 +2802,11 @@
           <t>Mes 2</t>
         </is>
       </c>
-      <c r="F83" s="5" t="inlineStr"/>
+      <c r="F83" s="10" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
     </row>
     <row r="84"/>
     <row r="85" ht="22" customHeight="1">
@@ -2476,7 +2840,11 @@
           <t>Mes 1-2</t>
         </is>
       </c>
-      <c r="F86" s="5" t="inlineStr"/>
+      <c r="F86" s="10" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="5" t="inlineStr">
@@ -2502,7 +2870,11 @@
           <t>Mes 2-4</t>
         </is>
       </c>
-      <c r="F87" s="5" t="inlineStr"/>
+      <c r="F87" s="10" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" s="5" t="inlineStr">
@@ -2528,7 +2900,11 @@
           <t>Mes 2-4</t>
         </is>
       </c>
-      <c r="F88" s="5" t="inlineStr"/>
+      <c r="F88" s="10" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" s="5" t="inlineStr">
@@ -2554,7 +2930,11 @@
           <t>Mes 1-2</t>
         </is>
       </c>
-      <c r="F89" s="5" t="inlineStr"/>
+      <c r="F89" s="10" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="5" t="inlineStr">
@@ -2580,7 +2960,11 @@
           <t>Mes 1-2</t>
         </is>
       </c>
-      <c r="F90" s="5" t="inlineStr"/>
+      <c r="F90" s="10" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" s="5" t="inlineStr">
@@ -2606,7 +2990,11 @@
           <t>Mes 1-2</t>
         </is>
       </c>
-      <c r="F91" s="5" t="inlineStr"/>
+      <c r="F91" s="10" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" s="5" t="inlineStr">
@@ -2632,7 +3020,11 @@
           <t>Mes 2-3</t>
         </is>
       </c>
-      <c r="F92" s="5" t="inlineStr"/>
+      <c r="F92" s="10" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" s="5" t="inlineStr">
@@ -2658,7 +3050,11 @@
           <t>Mes 2-4</t>
         </is>
       </c>
-      <c r="F93" s="5" t="inlineStr"/>
+      <c r="F93" s="10" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" s="5" t="inlineStr">
@@ -2684,7 +3080,11 @@
           <t>Mes 3-4</t>
         </is>
       </c>
-      <c r="F94" s="5" t="inlineStr"/>
+      <c r="F94" s="10" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" s="5" t="inlineStr">
@@ -2710,7 +3110,11 @@
           <t>Mes 2+</t>
         </is>
       </c>
-      <c r="F95" s="5" t="inlineStr"/>
+      <c r="F95" s="10" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" s="5" t="inlineStr">
@@ -2736,7 +3140,11 @@
           <t>Mes 2+</t>
         </is>
       </c>
-      <c r="F96" s="5" t="inlineStr"/>
+      <c r="F96" s="10" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" s="5" t="inlineStr">
@@ -2762,7 +3170,11 @@
           <t>Mes 3+</t>
         </is>
       </c>
-      <c r="F97" s="5" t="inlineStr"/>
+      <c r="F97" s="10" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" s="5" t="inlineStr">
@@ -2788,7 +3200,11 @@
           <t>Permanente</t>
         </is>
       </c>
-      <c r="F98" s="5" t="inlineStr"/>
+      <c r="F98" s="10" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" s="5" t="inlineStr">
@@ -2814,7 +3230,11 @@
           <t>Mes 6+</t>
         </is>
       </c>
-      <c r="F99" s="5" t="inlineStr"/>
+      <c r="F99" s="10" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
     </row>
     <row r="100"/>
     <row r="101" ht="22" customHeight="1">
@@ -2848,7 +3268,11 @@
           <t>Mín. 30 días antes</t>
         </is>
       </c>
-      <c r="F102" s="5" t="inlineStr"/>
+      <c r="F102" s="10" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" s="5" t="inlineStr">
@@ -2874,7 +3298,11 @@
           <t>Mín. 21 días antes</t>
         </is>
       </c>
-      <c r="F103" s="5" t="inlineStr"/>
+      <c r="F103" s="10" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" s="5" t="inlineStr">
@@ -2900,7 +3328,11 @@
           <t>Mín. 30 días antes</t>
         </is>
       </c>
-      <c r="F104" s="5" t="inlineStr"/>
+      <c r="F104" s="10" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" s="5" t="inlineStr">
@@ -2926,7 +3358,11 @@
           <t>Mín. 30 días antes</t>
         </is>
       </c>
-      <c r="F105" s="5" t="inlineStr"/>
+      <c r="F105" s="10" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" s="5" t="inlineStr">
@@ -2952,7 +3388,11 @@
           <t>5-7 días antes</t>
         </is>
       </c>
-      <c r="F106" s="5" t="inlineStr"/>
+      <c r="F106" s="10" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" s="5" t="inlineStr">
@@ -2978,7 +3418,11 @@
           <t>D-1</t>
         </is>
       </c>
-      <c r="F107" s="5" t="inlineStr"/>
+      <c r="F107" s="10" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" s="5" t="inlineStr">
@@ -3004,7 +3448,11 @@
           <t>D-1</t>
         </is>
       </c>
-      <c r="F108" s="5" t="inlineStr"/>
+      <c r="F108" s="10" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" s="5" t="inlineStr">
@@ -3030,7 +3478,11 @@
           <t>D</t>
         </is>
       </c>
-      <c r="F109" s="5" t="inlineStr"/>
+      <c r="F109" s="10" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" s="5" t="inlineStr">
@@ -3056,7 +3508,11 @@
           <t>D</t>
         </is>
       </c>
-      <c r="F110" s="5" t="inlineStr"/>
+      <c r="F110" s="10" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" s="5" t="inlineStr">
@@ -3082,7 +3538,11 @@
           <t>D</t>
         </is>
       </c>
-      <c r="F111" s="5" t="inlineStr"/>
+      <c r="F111" s="10" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" s="5" t="inlineStr">
@@ -3108,7 +3568,11 @@
           <t>D</t>
         </is>
       </c>
-      <c r="F112" s="5" t="inlineStr"/>
+      <c r="F112" s="10" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" s="5" t="inlineStr">
@@ -3134,7 +3598,11 @@
           <t>D</t>
         </is>
       </c>
-      <c r="F113" s="5" t="inlineStr"/>
+      <c r="F113" s="10" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" s="5" t="inlineStr">
@@ -3160,7 +3628,11 @@
           <t>D</t>
         </is>
       </c>
-      <c r="F114" s="5" t="inlineStr"/>
+      <c r="F114" s="10" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" s="5" t="inlineStr">
@@ -3186,7 +3658,11 @@
           <t>D+1-2</t>
         </is>
       </c>
-      <c r="F115" s="5" t="inlineStr"/>
+      <c r="F115" s="10" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" s="5" t="inlineStr">
@@ -3212,7 +3688,11 @@
           <t>D+2</t>
         </is>
       </c>
-      <c r="F116" s="5" t="inlineStr"/>
+      <c r="F116" s="10" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" s="5" t="inlineStr">
@@ -3238,7 +3718,11 @@
           <t>D+2-7</t>
         </is>
       </c>
-      <c r="F117" s="5" t="inlineStr"/>
+      <c r="F117" s="10" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" s="5" t="inlineStr">
@@ -3264,7 +3748,11 @@
           <t>D+2-3</t>
         </is>
       </c>
-      <c r="F118" s="5" t="inlineStr"/>
+      <c r="F118" s="10" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" s="5" t="inlineStr">
@@ -3290,19 +3778,33 @@
           <t>D+7</t>
         </is>
       </c>
-      <c r="F119" s="5" t="inlineStr"/>
+      <c r="F119" s="10" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="8">
-    <mergeCell ref="A2:J2"/>
+    <mergeCell ref="A38:F38"/>
+    <mergeCell ref="A1:J1"/>
     <mergeCell ref="A85:F85"/>
     <mergeCell ref="A5:F5"/>
     <mergeCell ref="A101:F101"/>
-    <mergeCell ref="A38:F38"/>
     <mergeCell ref="A67:F67"/>
+    <mergeCell ref="A2:J2"/>
     <mergeCell ref="A26:F26"/>
-    <mergeCell ref="A1:J1"/>
   </mergeCells>
+  <conditionalFormatting sqref="F6:F119">
+    <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
+      <formula>"✓"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="1">
+    <dataValidation sqref="F6:F119" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Estado del hito" error="Elige ✓ (hecho), ☐ (pendiente) o N/A (no aplica)." type="list" errorStyle="stop">
+      <formula1>"✓,☐,N/A"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>

--- a/astro-site/public/dl/plan-negocio-paellero-eventos/checklist-apertura-paellero-eventos.xlsx
+++ b/astro-site/public/dl/plan-negocio-paellero-eventos/checklist-apertura-paellero-eventos.xlsx
@@ -1130,7 +1130,7 @@
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>Puntos críticos: frío del marisco y la carne en el transporte, cocción y servicio a 63 °C o más (art. 30 del RD 1086/2020) y alioli con huevo pasteurizado o sin huevo. Nunca arroz tibio a temperatura ambiente</t>
+          <t>Puntos críticos: frío del marisco y la carne en el transporte, cocción y servicio a 63 °C o más (art. 30 del RD 1086/2020) y alioli con huevo pasteurizado o sin huevo. Nunca arroz tibio a temperatura ambiente. Guarda una comida testigo de cada arroz (100 g, identificada y fechada, a 4 °C o menos o congelada, 7 días): obligatoria en eventos de más de 40 personas y si los eventos son tu actividad principal (art. 30.8 y 30.10 del RD 1086/2020)</t>
         </is>
       </c>
     </row>
@@ -2720,7 +2720,7 @@
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
-          <t>Lista de los planners de tu zona y un correo personal a cada uno (anexo del plan de negocio)</t>
+          <t>Lista de los planners de tu zona y un correo personal a cada uno (sección 5 del plan de negocio)</t>
         </is>
       </c>
     </row>
@@ -2801,7 +2801,7 @@
       </c>
       <c r="E18" s="5" t="inlineStr">
         <is>
-          <t>Un ayuntamiento compra por contrato menor (servicios de menos de 15.000 €, Ley 9/2017 art. 118) y paga a 30 días desde la conformidad (art. 198.4). Si eres SL, la factura va en electrónico por FACe (Ley 25/2013, art. 4). Alta en la Plataforma de Contratación para ver las licitaciones</t>
+          <t>Un ayuntamiento compra por contrato menor (servicios de menos de 15.000 €, Ley 9/2017 art. 118) y paga a 30 días desde la conformidad (art. 198.4), sin anticipo. Si eres SL, la factura va en electrónico a su punto general de entrada (FACe en la mayoría; Ley 25/2013, art. 4), salvo que exima las de hasta 5.000 €. Alta en la Plataforma de Contratación para ver las licitaciones</t>
         </is>
       </c>
     </row>
@@ -3043,7 +3043,7 @@
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>Sin anticipo no se bloquea la fecha. Particulares: el 70 % restante el día del evento; empresas: a 30 días de la factura. En efectivo, sólo hasta 1.000 € con particulares (Ley 7/2012, art. 7)</t>
+          <t>Sin anticipo no se bloquea la fecha. Particulares: el 70 % restante el día del evento; empresas: a 30 días de la factura. En efectivo, sólo pagos por debajo de 1.000 € (Ley 7/2012, art. 7). Los ayuntamientos no adelantan: pagan a 30 días desde la conformidad</t>
         </is>
       </c>
     </row>
@@ -3259,7 +3259,7 @@
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
-          <t>Registro de temperaturas en el APPCC y servicio a 63 °C o más; nada de arroz tibio a temperatura ambiente</t>
+          <t>Registro de temperaturas en el APPCC y servicio a 63 °C o más; nada de arroz tibio a temperatura ambiente. Aparta la comida testigo de cada arroz (art. 30.8 del RD 1086/2020)</t>
         </is>
       </c>
     </row>
@@ -3313,7 +3313,7 @@
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>Particulares: el 70 % el día del evento. Empresas: a 30 días de la factura. Ayuntamientos: por FACe y a 30 días desde la conformidad</t>
+          <t>Particulares: el 70 % el día del evento. Empresas: a 30 días de la factura. Ayuntamientos: factura electrónica en su punto general de entrada (FACe en la mayoría, salvo que exima las de hasta 5.000 €) y cobro a 30 días desde la conformidad</t>
         </is>
       </c>
     </row>

--- a/astro-site/public/dl/plan-negocio-paellero-eventos/checklist-apertura-paellero-eventos.xlsx
+++ b/astro-site/public/dl/plan-negocio-paellero-eventos/checklist-apertura-paellero-eventos.xlsx
@@ -1130,7 +1130,7 @@
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>Puntos críticos: frío del marisco y la carne en el transporte, cocción y servicio a 63 °C o más (art. 30 del RD 1086/2020) y alioli con huevo pasteurizado o sin huevo. Nunca arroz tibio a temperatura ambiente. Guarda una comida testigo de cada arroz (100 g, identificada y fechada, a 4 °C o menos o congelada, 7 días): obligatoria en eventos de más de 40 personas y si los eventos son tu actividad principal (art. 30.8 y 30.10 del RD 1086/2020)</t>
+          <t>Puntos críticos: frío del marisco y la carne en el transporte, cocción y servicio a 63 °C o más (art. 30 del RD 1086/2020) y alioli con huevo pasteurizado o sin huevo. Nunca arroz tibio a temperatura ambiente. Guarda una comida testigo de cada arroz (100 g, identificada y fechada, a 4 °C o menos o congelada, 7 días): obligatoria en todos tus eventos, porque son tu actividad principal (art. 30.8.d del RD 1086/2020), y en cualquier encargo de más de 40 personas (30.8.e); conservación según el 30.10</t>
         </is>
       </c>
     </row>

--- a/astro-site/public/dl/plan-negocio-paellero-eventos/checklist-apertura-paellero-eventos.xlsx
+++ b/astro-site/public/dl/plan-negocio-paellero-eventos/checklist-apertura-paellero-eventos.xlsx
@@ -951,8 +951,8 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="A5 A6 A7 A8 A9 A10 A11 A12 A13 A14 A15 A16" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Marca no válida" error="Usa el desplegable: ✓, —, N/A. N/A = no aplica, sale del total." type="list">
-      <formula1>"✓,—,N/A"</formula1>
+    <dataValidation sqref="A5 A6 A7 A8 A9 A10 A11 A12 A13 A14 A15 A16" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Marca no válida" error="Usa el desplegable: ✓, ☐, N/A. N/A = no aplica, sale del total." type="list">
+      <formula1>"✓,☐,N/A"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
@@ -1490,8 +1490,8 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="A5 A6 A7 A8 A9 A10 A11 A12 A13 A14 A15 A16 A17 A18 A19 A20" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Marca no válida" error="Usa el desplegable: ✓, —, N/A. N/A = no aplica, sale del total." type="list">
-      <formula1>"✓,—,N/A"</formula1>
+    <dataValidation sqref="A5 A6 A7 A8 A9 A10 A11 A12 A13 A14 A15 A16 A17 A18 A19 A20" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Marca no válida" error="Usa el desplegable: ✓, ☐, N/A. N/A = no aplica, sale del total." type="list">
+      <formula1>"✓,☐,N/A"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
@@ -1975,8 +1975,8 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="A5 A6 A7 A8 A9 A10 A11 A12 A13 A14 A15 A16 A17 A18" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Marca no válida" error="Usa el desplegable: ✓, —, N/A. N/A = no aplica, sale del total." type="list">
-      <formula1>"✓,—,N/A"</formula1>
+    <dataValidation sqref="A5 A6 A7 A8 A9 A10 A11 A12 A13 A14 A15 A16 A17 A18" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Marca no válida" error="Usa el desplegable: ✓, ☐, N/A. N/A = no aplica, sale del total." type="list">
+      <formula1>"✓,☐,N/A"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
@@ -2352,8 +2352,8 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="A5 A6 A7 A8 A9 A10 A11 A12 A13 A14" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Marca no válida" error="Usa el desplegable: ✓, —, N/A. N/A = no aplica, sale del total." type="list">
-      <formula1>"✓,—,N/A"</formula1>
+    <dataValidation sqref="A5 A6 A7 A8 A9 A10 A11 A12 A13 A14" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Marca no válida" error="Usa el desplegable: ✓, ☐, N/A. N/A = no aplica, sale del total." type="list">
+      <formula1>"✓,☐,N/A"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
@@ -2891,8 +2891,8 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="A5 A6 A7 A8 A9 A10 A11 A12 A13 A14 A15 A16 A17 A18 A19 A20" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Marca no válida" error="Usa el desplegable: ✓, —, N/A. N/A = no aplica, sale del total." type="list">
-      <formula1>"✓,—,N/A"</formula1>
+    <dataValidation sqref="A5 A6 A7 A8 A9 A10 A11 A12 A13 A14 A15 A16 A17 A18 A19 A20" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Marca no válida" error="Usa el desplegable: ✓, ☐, N/A. N/A = no aplica, sale del total." type="list">
+      <formula1>"✓,☐,N/A"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
@@ -3403,8 +3403,8 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="A5 A6 A7 A8 A9 A10 A11 A12 A13 A14 A15 A16 A17 A18 A19" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Marca no válida" error="Usa el desplegable: ✓, —, N/A. N/A = no aplica, sale del total." type="list">
-      <formula1>"✓,—,N/A"</formula1>
+    <dataValidation sqref="A5 A6 A7 A8 A9 A10 A11 A12 A13 A14 A15 A16 A17 A18 A19" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Marca no válida" error="Usa el desplegable: ✓, ☐, N/A. N/A = no aplica, sale del total." type="list">
+      <formula1>"✓,☐,N/A"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
